--- a/data/example.xlsx
+++ b/data/example.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>query</t>
   </si>
@@ -37,7 +37,19 @@
     <t>What is the difference between HTTP and HTTPS?</t>
   </si>
   <si>
-    <t>{"model": "PLACEHOLDER_MODEL", "messages": [{"role": "system", "content": "{{system_prompt}}"}, {"role": "user", "content": "{{query}}"}]}</t>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] 什么是机器学习？"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] Python中list和tuple的区别是什么？"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] Explain the concept of recursion."}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] 如何用Docker部署一个Python应用？"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] What is the difference between HTTP and HTTPS?"}]</t>
   </si>
 </sst>
 </file>
@@ -393,7 +405,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -401,7 +413,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -409,7 +421,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -417,7 +429,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/example.xlsx
+++ b/data/example.xlsx
@@ -1,52 +1,237 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+  <si>
+    <t>idx</t>
+  </si>
   <si>
     <t>query</t>
   </si>
   <si>
+    <t>response</t>
+  </si>
+  <si>
     <t>api_json</t>
   </si>
   <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>sub_domain</t>
+  </si>
+  <si>
     <t>什么是机器学习？</t>
   </si>
   <si>
+    <t>机器学习是人工智能的一个核心分支，它让计算机通过数据“学习”规律，而无需人为编写明确的规则。简单来说，就是利用算法从大量数据中自动发现模式，并用这些模式对未知数据做出预测或决策。
+其基本思想是：给定一组训练数据（包含输入和期望输出），算法通过迭代优化来调整内部参数，使得模型在新数据上也能表现良好。这个过程类似于人类通过经验积累提升技能。
+**主要类型包括：**
+- **监督学习**：使用带标签的数据（如“猫/狗”图片）训练模型，用于分类或回归任务。
+- **无监督学习**：处理无标签数据，自动发现数据中的隐藏结构（如聚类、降维）。
+- **强化学习**：让智能体通过与环境互动、获得奖励或惩罚来学习最优策略（如围棋、自动驾驶）。
+**常见应用**：推荐系统（抖音/Netflix）、语音助手（Siri）、人脸识别、医疗诊断、自然语言处理（ChatGPT）等。机器学习如今已渗透到日常生活与各行各业。</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] 什么是机器学习？"}]</t>
+  </si>
+  <si>
+    <t>knowledge_qa</t>
+  </si>
+  <si>
     <t>Python中list和tuple的区别是什么？</t>
   </si>
   <si>
+    <t>在 Python 中，`list`（列表）和 `tuple`（元组）都是序列类型，但有几个关键区别：
+1. **可变性**  
+   - `list` 是**可变**的（mutable），可以修改、添加、删除元素。  
+   - `tuple` 是**不可变**的（immutable），一旦创建就不能更改其内容（不能增删改元素）。
+2. **语法**  
+   - `list` 使用方括号 `[]`，例如 `[1, 2, 3]`。  
+   - `tuple` 使用圆括号 `()`，例如 `(1, 2, 3)`，但逗号是必须的，单元素元组需加逗号如 `(1,)`。
+3. **性能**  
+   - `tuple` 的不可变性使其在创建和访问时稍快，且占用内存更小（因为不需要预留修改空间）。  
+   - `list` 由于支持动态修改，会额外分配内存以支持扩容。
+4. **用途**  
+   - `list` 适合存储需要修改的同类数据，如待办列表、动态集合。  
+   - `tuple` 适合表示固定结构的数据，如坐标、数据库记录、函数多返回值，也可作为字典键（因为可哈希）。
+5. **方法**  
+   - `list` 有大量修改方法（如 `append()`、`pop()`、`insert()`）。  
+   - `tuple` 只有 `count()` 和 `index()` 等查询方法。
+6. **可哈希性**  
+   - `list` 不可哈希（unhashable），不能作为字典键或集合元素。  
+   - `tuple` 若元素都是可哈希的，则本身可哈希，可用作字典键。
+简单总结：**list 可变，tuple 不可变；list 用 `[]`，tuple 用 `()`；list 适合动态集合，tuple 适合固定不变的数据。**</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] Python中list和tuple的区别是什么？"}]</t>
+  </si>
+  <si>
     <t>Explain the concept of recursion.</t>
   </si>
   <si>
+    <t>**Recursion** is a programming technique where a function calls itself to solve a problem by breaking it down into smaller, similar subproblems. It’s like a set of Russian dolls – each doll contains a smaller version of itself until you reach the smallest one.
+### Key components of a recursive function:
+1. **Base case** – a condition that stops the recursion. Without it, the function would call itself forever (leading to a stack overflow).
+2. **Recursive case** – the part where the function calls itself with a modified argument, moving toward the base case.
+### Classic example: Factorial
+The factorial of a non-negative integer `n` (written `n!`) is the product of all positive integers less than or equal to `n`.  
+- Definition: `n! = n * (n-1)!`  
+- Base case: `0! = 1`
+```python
+def factorial(n):
+    if n == 0:          # base case
+        return 1
+    else:               # recursive case
+        return n * factorial(n - 1)
+```
+For `factorial(3)`:
+- `3 * factorial(2)`
+- `2 * factorial(1)`
+- `1 * factorial(0)`
+- returns `1`
+- then `1 * 1 = 1`, `2 * 1 = 2`, `3 * 2 = 6`
+### How it works behind the scenes
+Each recursive call is placed on the **call stack** – a data structure that keeps track of pending function calls. When the base case is reached, the stack unwinds and each call returns its result to the previous one.
+### When to use recursion
+- Problems that can be naturally divided into similar subproblems (e.g., tree traversal, divide-and-conquer algorithms, backtracking)
+- Problems with a recursive mathematical definition (e.g., Fibonacci, permutations)
+### Potential pitfalls
+- **Stack overflow** – if recursion depth is too large (e.g., millions of calls)
+- **Redundant calculations** – e.g., naive Fibonacci recursion recalculates the same values many times; this can be fixed with memoization or iteration.
+In short: recursion is a powerful tool for solving problems that have a repetitive, self-similar structure, but it must be used with care to avoid performance or memory issues.</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] Explain the concept of recursion."}]</t>
+  </si>
+  <si>
     <t>如何用Docker部署一个Python应用？</t>
   </si>
   <si>
+    <t>使用 Docker 部署 Python 应用通常包括以下步骤：
+### 1. 项目准备
+确保你的 Python 应用有以下文件：
+- `requirements.txt`（依赖列表）
+- 主脚本（例如 `app.py`）
+### 2. 创建 `Dockerfile`
+在项目根目录创建无后缀的 `Dockerfile`，示例如下：
+```dockerfile
+# 使用官方 Python 运行时作为基础镜像
+FROM python:3.11-slim
+# 设置工作目录
+WORKDIR /app
+# 将依赖文件复制到容器
+COPY requirements.txt .
+# 安装依赖
+RUN pip install --no-cache-dir -r requirements.txt
+# 将项目代码复制到容器
+COPY . .
+# 暴露端口（如果你的应用监听某个端口，如 Flask 默认 5000）
+EXPOSE 5000
+# 定义容器启动时执行的命令
+CMD ["python", "app.py"]
+```
+### 3. 构建 Docker 镜像
+在项目根目录下执行：
+```bash
+docker build -t my-python-app .
+```
+`-t` 参数给镜像命名（如 `my-python-app`），最后的 `.` 表示当前目录。
+### 4. 运行容器
+```bash
+docker run -p 8000:5000 my-python-app
+```
+- `-p 8000:5000`：将本机的 8000 端口映射到容器的 5000 端口（根据你的应用实际端口调整）
+- 如果应用需要交互，可添加 `-it` 参数
+### 5. 可选：使用 `docker-compose`（推荐）
+如果应用依赖数据库、缓存等服务，可以创建 `docker-compose.yml` 文件：
+```yaml
+version: '3'
+services:
+  web:
+    build: .
+    ports:
+      - "8000:5000"
+    depends_on:
+      - db
+  db:
+    image: postgres:13
+    environment:
+      POSTGRES_DB: mydb
+      POSTGRES_USER: user
+      POSTGRES_PASSWORD: pass
+```
+然后使用 `docker-compose up` 一键启动所有服务。
+### 注意事项
+- 尽量使用 `slim` 或 `alpine` 版本的基础镜像，减小体积
+- 使用 `.dockerignore` 文件忽略不必要的文件（如 `__pycache__`、`.env`、`venv` 等）
+- 生产环境建议使用非 root 用户运行（可在 Dockerfile 中添加 `RUN useradd -m myuser` 和 `USER myuser`）
+通过以上步骤，你就可以轻松将 Python 应用容器化并部署了。</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] 如何用Docker部署一个Python应用？"}]</t>
+  </si>
+  <si>
     <t>What is the difference between HTTP and HTTPS?</t>
   </si>
   <si>
-    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] 什么是机器学习？"}]</t>
-  </si>
-  <si>
-    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] Python中list和tuple的区别是什么？"}]</t>
-  </si>
-  <si>
-    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] Explain the concept of recursion."}]</t>
-  </si>
-  <si>
-    <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] 如何用Docker部署一个Python应用？"}]</t>
+    <t>**HTTP** (HyperText Transfer Protocol) and **HTTPS** (HyperText Transfer Protocol Secure) are both protocols used to transfer data between a web browser and a website. The key difference is **security**.
+---
+### 1. Encryption
+- **HTTP**: Data is sent in **plain text**. Anyone who intercepts the communication (e.g., on public Wi-Fi) can read the data, including passwords, credit card numbers, or personal messages.
+- **HTTPS**: Data is **encrypted** using **SSL/TLS** (Secure Sockets Layer / Transport Layer Security). Even if intercepted, the data appears as scrambled, unreadable text.
+### 2. Authentication
+- **HTTP**: No mechanism to verify that you are talking to the real website. A malicious actor could impersonate a site (man-in-the-middle attack).
+- **HTTPS**: Uses **digital certificates** issued by trusted Certificate Authorities (CAs). The browser verifies that the certificate matches the domain, confirming you are connected to the genuine website.
+### 3. Port Numbers
+- **HTTP** typically uses **port 80**.
+- **HTTPS** typically uses **port 443**.
+### 4. URL Prefix &amp; Browser Indicators
+- **HTTP**: URLs start with `http://`. Browsers may show a “Not secure” warning or a gray lock icon.
+- **HTTPS**: URLs start with `https://`. Browsers display a **padlock icon**, and sometimes the company name (for Extended Validation certificates). Green indicators signal a secure connection.
+### 5. Performance
+- **HTTPS** used to be slower due to encryption overhead, but modern implementations (like **TLS 1.3** and HTTP/2) make it nearly as fast as HTTP, often faster due to optimizations.
+### 6. SEO &amp; Trust
+- Search engines (like Google) **favor HTTPS** sites, giving them a ranking boost.
+- Users are more likely to trust and enter sensitive information on an HTTPS site.
+---
+## Summary Table
+| Feature             | HTTP                              | HTTPS                                    |
+|---------------------|-----------------------------------|------------------------------------------|
+| Encryption          | None (plain text)                 | SSL/TLS encryption (data is scrambled)   |
+| Data Integrity      | Data can be tampered              | Tampering is detectable                  |
+| Authentication      | No identity verification          | Verified via SSL certificate             |
+| Default Port        | 80                                | 443                                      |
+| Browser Indicator   | "Not secure" warning              | Padlock icon, "Secure" label             |
+| Use Cases           | Non-sensitive, public content     | Logins, payments, personal data, any modern site |
+---
+**Bottom line:** Always use HTTPS for any website that handles sensitive information. For most websites today, HTTPS is the standard and expected.</t>
   </si>
   <si>
     <t>[{"role": "system", "content": ""}, {"role": "user", "content": "[Current Time: 2024-06-01 14:30:00 CST] What is the difference between HTTP and HTTPS?"}]</t>
@@ -55,25 +240,376 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -81,18 +617,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -375,64 +1207,129 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="45.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="53.4545454545455" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="25.4545454545455" customWidth="1"/>
+    <col min="6" max="6" width="23.0909090909091" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>